--- a/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣觀光景點上下車人數及百分比前三名及後三名路線.xlsx
+++ b/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣觀光景點上下車人數及百分比前三名及後三名路線.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t xml:space="preserve">景點...1</t>
   </si>
@@ -101,6 +101,36 @@
     <t xml:space="preserve">Bottom3</t>
   </si>
   <si>
+    <t xml:space="preserve">加路蘭遊憩區</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.45%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.19%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22%</t>
+  </si>
+  <si>
     <t xml:space="preserve">池上車站</t>
   </si>
   <si>
@@ -134,7 +164,7 @@
     <t xml:space="preserve">25.76%</t>
   </si>
   <si>
-    <t xml:space="preserve">卑南初鹿地區</t>
+    <t xml:space="preserve">初鹿地區</t>
   </si>
   <si>
     <t xml:space="preserve">29.13%</t>
@@ -167,9 +197,6 @@
     <t xml:space="preserve">都蘭遊憩區</t>
   </si>
   <si>
-    <t xml:space="preserve">8103</t>
-  </si>
-  <si>
     <t xml:space="preserve">30.11%</t>
   </si>
   <si>
@@ -177,9 +204,6 @@
   </si>
   <si>
     <t xml:space="preserve">30.07%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8122</t>
   </si>
   <si>
     <t xml:space="preserve">5.74%</t>
@@ -758,13 +782,13 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9475</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3003</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -773,13 +797,13 @@
         <v>29</v>
       </c>
       <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
         <v>32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>103</v>
-      </c>
-      <c r="I5" t="s">
-        <v>33</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -790,13 +814,13 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2937</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -805,13 +829,13 @@
         <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>1659</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
@@ -822,13 +846,13 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>2673</v>
+        <v>549</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -837,13 +861,13 @@
         <v>29</v>
       </c>
       <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="n">
+        <v>261</v>
+      </c>
+      <c r="I7" t="s">
         <v>38</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2673</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
@@ -851,13 +875,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
       <c r="C8" t="n">
-        <v>10037</v>
+        <v>3003</v>
       </c>
       <c r="D8" t="s">
         <v>41</v>
@@ -866,13 +890,13 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
       <c r="H8" t="n">
-        <v>1826</v>
+        <v>103</v>
       </c>
       <c r="I8" t="s">
         <v>43</v>
@@ -883,13 +907,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>5738</v>
+        <v>2937</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -898,13 +922,13 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
         <v>46</v>
       </c>
       <c r="H9" t="n">
-        <v>2245</v>
+        <v>1659</v>
       </c>
       <c r="I9" t="s">
         <v>47</v>
@@ -915,28 +939,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>5388</v>
+        <v>2673</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H10" t="n">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -950,13 +974,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10037</v>
+      </c>
+      <c r="D11" t="s">
         <v>51</v>
-      </c>
-      <c r="C11" t="n">
-        <v>17685</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -965,10 +989,10 @@
         <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="H11" t="n">
-        <v>1637</v>
+        <v>1826</v>
       </c>
       <c r="I11" t="s">
         <v>53</v>
@@ -982,13 +1006,13 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C12" t="n">
-        <v>17664</v>
+        <v>5738</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -997,13 +1021,13 @@
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" t="n">
-        <v>3369</v>
+        <v>2245</v>
       </c>
       <c r="I12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -1014,13 +1038,13 @@
         <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
-        <v>7595</v>
+        <v>5388</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
@@ -1029,10 +1053,10 @@
         <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H13" t="n">
-        <v>4991</v>
+        <v>2669</v>
       </c>
       <c r="I13" t="s">
         <v>59</v>
@@ -1046,10 +1070,10 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>1697</v>
+        <v>17685</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -1061,13 +1085,13 @@
         <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>1697</v>
+        <v>1637</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J14" t="s">
         <v>16</v>
@@ -1077,18 +1101,30 @@
       <c r="A15" t="s">
         <v>60</v>
       </c>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="n">
+        <v>17664</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
         <v>60</v>
       </c>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3369</v>
+      </c>
+      <c r="I15" t="s">
+        <v>64</v>
+      </c>
       <c r="J15" t="s">
         <v>22</v>
       </c>
@@ -1097,49 +1133,61 @@
       <c r="A16" t="s">
         <v>60</v>
       </c>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7595</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
       <c r="E16" t="s">
         <v>25</v>
       </c>
       <c r="F16" t="s">
         <v>60</v>
       </c>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4991</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
       <c r="J16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C17" t="n">
-        <v>43133</v>
+        <v>1697</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H17" t="n">
-        <v>105</v>
+        <v>1697</v>
       </c>
       <c r="I17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J17" t="s">
         <v>16</v>
@@ -1147,64 +1195,40 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27231</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="n">
-        <v>291</v>
-      </c>
-      <c r="I18" t="s">
-        <v>67</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
       <c r="J18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5429</v>
-      </c>
-      <c r="D19" t="s">
         <v>68</v>
       </c>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1599</v>
-      </c>
-      <c r="I19" t="s">
-        <v>69</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
       <c r="J19" t="s">
         <v>28</v>
       </c>
@@ -1214,13 +1238,13 @@
         <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C20" t="n">
-        <v>66266</v>
+        <v>43133</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
@@ -1229,10 +1253,10 @@
         <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="H20" t="n">
-        <v>5161</v>
+        <v>105</v>
       </c>
       <c r="I20" t="s">
         <v>73</v>
@@ -1249,7 +1273,7 @@
         <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>62053</v>
+        <v>27231</v>
       </c>
       <c r="D21" t="s">
         <v>74</v>
@@ -1261,13 +1285,13 @@
         <v>70</v>
       </c>
       <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>291</v>
+      </c>
+      <c r="I21" t="s">
         <v>75</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5589</v>
-      </c>
-      <c r="I21" t="s">
-        <v>76</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -1278,13 +1302,13 @@
         <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>60885</v>
+        <v>5429</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
@@ -1293,13 +1317,13 @@
         <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="H22" t="n">
-        <v>10475</v>
+        <v>1599</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s">
         <v>28</v>
@@ -1307,31 +1331,31 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C23" t="n">
-        <v>4123</v>
+        <v>66266</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
       </c>
       <c r="F23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" t="s">
         <v>80</v>
       </c>
-      <c r="G23" t="s">
-        <v>63</v>
-      </c>
       <c r="H23" t="n">
-        <v>680</v>
+        <v>5161</v>
       </c>
       <c r="I23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J23" t="s">
         <v>16</v>
@@ -1339,31 +1363,31 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>680</v>
+        <v>62053</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H24" t="n">
-        <v>4123</v>
+        <v>5589</v>
       </c>
       <c r="I24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -1371,51 +1395,63 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="n">
+        <v>60885</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
       <c r="E25" t="s">
         <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
-      </c>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
+        <v>78</v>
+      </c>
+      <c r="G25" t="s">
+        <v>54</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10475</v>
+      </c>
+      <c r="I25" t="s">
+        <v>87</v>
+      </c>
       <c r="J25" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26" t="n">
-        <v>111094</v>
+        <v>4123</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
         <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="H26" t="n">
-        <v>1177</v>
+        <v>680</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J26" t="s">
         <v>16</v>
@@ -1423,31 +1459,31 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="C27" t="n">
-        <v>56284</v>
+        <v>680</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4123</v>
+      </c>
+      <c r="I27" t="s">
         <v>90</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1402</v>
-      </c>
-      <c r="I27" t="s">
-        <v>91</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -1455,33 +1491,117 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="n">
-        <v>52135</v>
-      </c>
-      <c r="D28" t="s">
-        <v>92</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
       <c r="E28" t="s">
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s">
         <v>93</v>
       </c>
-      <c r="H28" t="n">
+      <c r="C29" t="n">
+        <v>111094</v>
+      </c>
+      <c r="D29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1177</v>
+      </c>
+      <c r="I29" t="s">
+        <v>96</v>
+      </c>
+      <c r="J29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="n">
+        <v>56284</v>
+      </c>
+      <c r="D30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1402</v>
+      </c>
+      <c r="I30" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" t="n">
+        <v>52135</v>
+      </c>
+      <c r="D31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" t="s">
+        <v>101</v>
+      </c>
+      <c r="H31" t="n">
         <v>2210</v>
       </c>
-      <c r="I28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="I31" t="s">
+        <v>102</v>
+      </c>
+      <c r="J31" t="s">
         <v>28</v>
       </c>
     </row>

--- a/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣觀光景點上下車人數及百分比前三名及後三名路線.xlsx
+++ b/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣觀光景點上下車人數及百分比前三名及後三名路線.xlsx
@@ -1,340 +1,442 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\交通觀光景點分析 + 鄉鎮際搭乘分析\datasets\112-114\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2787CBF8-8B00-493D-AA3D-689A9C1D76F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="臺東縣觀光景點上下車人數及百分比前三名及後三名路線" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="臺東縣觀光景點上下車人數及百分比前三名及後三名路線" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
-  <si>
-    <t xml:space="preserve">景點...1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">路線...2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人數...3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">百分比...4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">類別...5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">景點...6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">路線...7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人數...8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">百分比...9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">類別...10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三仙台遊憩區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottom1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottom2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottom3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加路蘭遊憩區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.45%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.19%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">池上車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.94%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.31%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.99%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.76%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">初鹿地區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.13%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.66%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.64%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">都蘭遊憩區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.11%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.07%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.93%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鹿野高台</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">富岡漁港及小野柳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陸海空線</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.99%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">臺東車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.08%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.68%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">市區循環</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.29%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">臺東航空站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.84%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.16%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">臺東轉運站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.24%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38%</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="110">
+  <si>
+    <t>景點...1</t>
+  </si>
+  <si>
+    <t>路線...2</t>
+  </si>
+  <si>
+    <t>人數...3</t>
+  </si>
+  <si>
+    <t>百分比...4</t>
+  </si>
+  <si>
+    <t>類別...5</t>
+  </si>
+  <si>
+    <t>景點...6</t>
+  </si>
+  <si>
+    <t>路線...7</t>
+  </si>
+  <si>
+    <t>人數...8</t>
+  </si>
+  <si>
+    <t>百分比...9</t>
+  </si>
+  <si>
+    <t>類別...10</t>
+  </si>
+  <si>
+    <t>三仙台遊憩區</t>
+  </si>
+  <si>
+    <t>8101</t>
+  </si>
+  <si>
+    <t>59.6%</t>
+  </si>
+  <si>
+    <t>Top1</t>
+  </si>
+  <si>
+    <t>8119</t>
+  </si>
+  <si>
+    <t>4.79%</t>
+  </si>
+  <si>
+    <t>Bottom1</t>
+  </si>
+  <si>
+    <t>1145</t>
+  </si>
+  <si>
+    <t>14.8%</t>
+  </si>
+  <si>
+    <t>Top2</t>
+  </si>
+  <si>
+    <t>8181</t>
+  </si>
+  <si>
+    <t>5.09%</t>
+  </si>
+  <si>
+    <t>Bottom2</t>
+  </si>
+  <si>
+    <t>8105</t>
+  </si>
+  <si>
+    <t>8.27%</t>
+  </si>
+  <si>
+    <t>Top3</t>
+  </si>
+  <si>
+    <t>8102</t>
+  </si>
+  <si>
+    <t>7.45%</t>
+  </si>
+  <si>
+    <t>Bottom3</t>
+  </si>
+  <si>
+    <t>加路蘭遊憩區</t>
+  </si>
+  <si>
+    <t>80.45%</t>
+  </si>
+  <si>
+    <t>8122</t>
+  </si>
+  <si>
+    <t>0.01%</t>
+  </si>
+  <si>
+    <t>8103</t>
+  </si>
+  <si>
+    <t>9.34%</t>
+  </si>
+  <si>
+    <t>0.19%</t>
+  </si>
+  <si>
+    <t>4.66%</t>
+  </si>
+  <si>
+    <t>8120</t>
+  </si>
+  <si>
+    <t>2.22%</t>
+  </si>
+  <si>
+    <t>池上車站</t>
+  </si>
+  <si>
+    <t>8161</t>
+  </si>
+  <si>
+    <t>28.94%</t>
+  </si>
+  <si>
+    <t>8173</t>
+  </si>
+  <si>
+    <t>0.99%</t>
+  </si>
+  <si>
+    <t>8165</t>
+  </si>
+  <si>
+    <t>28.31%</t>
+  </si>
+  <si>
+    <t>8166</t>
+  </si>
+  <si>
+    <t>15.99%</t>
+  </si>
+  <si>
+    <t>8163</t>
+  </si>
+  <si>
+    <t>25.76%</t>
+  </si>
+  <si>
+    <t>初鹿地區</t>
+  </si>
+  <si>
+    <t>29.13%</t>
+  </si>
+  <si>
+    <t>8170</t>
+  </si>
+  <si>
+    <t>5.3%</t>
+  </si>
+  <si>
+    <t>8168</t>
+  </si>
+  <si>
+    <t>16.66%</t>
+  </si>
+  <si>
+    <t>8167</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>15.64%</t>
+  </si>
+  <si>
+    <t>7.75%</t>
+  </si>
+  <si>
+    <t>都蘭遊憩區</t>
+  </si>
+  <si>
+    <t>30.11%</t>
+  </si>
+  <si>
+    <t>2.79%</t>
+  </si>
+  <si>
+    <t>30.07%</t>
+  </si>
+  <si>
+    <t>5.74%</t>
+  </si>
+  <si>
+    <t>12.93%</t>
+  </si>
+  <si>
+    <t>8109</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>鹿野高台</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>富岡漁港及小野柳</t>
+  </si>
+  <si>
+    <t>陸海空線</t>
+  </si>
+  <si>
+    <t>52.25%</t>
+  </si>
+  <si>
+    <t>0.13%</t>
+  </si>
+  <si>
+    <t>32.99%</t>
+  </si>
+  <si>
+    <t>0.35%</t>
+  </si>
+  <si>
+    <t>6.58%</t>
+  </si>
+  <si>
+    <t>1.94%</t>
+  </si>
+  <si>
+    <t>臺東車站</t>
+  </si>
+  <si>
+    <t>22.08%</t>
+  </si>
+  <si>
+    <t>8115</t>
+  </si>
+  <si>
+    <t>1.72%</t>
+  </si>
+  <si>
+    <t>20.68%</t>
+  </si>
+  <si>
+    <t>8117</t>
+  </si>
+  <si>
+    <t>1.86%</t>
+  </si>
+  <si>
+    <t>市區循環</t>
+  </si>
+  <si>
+    <t>20.29%</t>
+  </si>
+  <si>
+    <t>3.49%</t>
+  </si>
+  <si>
+    <t>臺東航空站</t>
+  </si>
+  <si>
+    <t>8128</t>
+  </si>
+  <si>
+    <t>85.84%</t>
+  </si>
+  <si>
+    <t>14.16%</t>
+  </si>
+  <si>
+    <t>臺東轉運站</t>
+  </si>
+  <si>
+    <t>8129</t>
+  </si>
+  <si>
+    <t>19.24%</t>
+  </si>
+  <si>
+    <t>8131</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>9.75%</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>0.24%</t>
+  </si>
+  <si>
+    <t>9.03%</t>
+  </si>
+  <si>
+    <t>8130</t>
+  </si>
+  <si>
+    <t>0.38%</t>
+  </si>
+  <si>
+    <t>景點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下車人數前三名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>下車人數</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>三名</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>富岡漁港及小野柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -357,13 +459,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -645,11 +765,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -681,14 +801,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>11033</v>
       </c>
       <c r="D2" t="s">
@@ -703,7 +823,7 @@
       <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>886</v>
       </c>
       <c r="I2" t="s">
@@ -713,14 +833,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2740</v>
       </c>
       <c r="D3" t="s">
@@ -735,7 +855,7 @@
       <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>942</v>
       </c>
       <c r="I3" t="s">
@@ -745,14 +865,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1531</v>
       </c>
       <c r="D4" t="s">
@@ -767,7 +887,7 @@
       <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>1379</v>
       </c>
       <c r="I4" t="s">
@@ -777,14 +897,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9475</v>
       </c>
       <c r="D5" t="s">
@@ -799,7 +919,7 @@
       <c r="G5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5" t="s">
@@ -809,14 +929,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>1100</v>
       </c>
       <c r="D6" t="s">
@@ -831,7 +951,7 @@
       <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>22</v>
       </c>
       <c r="I6" t="s">
@@ -841,14 +961,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>549</v>
       </c>
       <c r="D7" t="s">
@@ -863,7 +983,7 @@
       <c r="G7" t="s">
         <v>37</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>261</v>
       </c>
       <c r="I7" t="s">
@@ -873,14 +993,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>39</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>3003</v>
       </c>
       <c r="D8" t="s">
@@ -895,7 +1015,7 @@
       <c r="G8" t="s">
         <v>42</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>103</v>
       </c>
       <c r="I8" t="s">
@@ -905,14 +1025,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>44</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2937</v>
       </c>
       <c r="D9" t="s">
@@ -927,7 +1047,7 @@
       <c r="G9" t="s">
         <v>46</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>1659</v>
       </c>
       <c r="I9" t="s">
@@ -937,14 +1057,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>2673</v>
       </c>
       <c r="D10" t="s">
@@ -959,7 +1079,7 @@
       <c r="G10" t="s">
         <v>48</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>2673</v>
       </c>
       <c r="I10" t="s">
@@ -969,14 +1089,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>50</v>
       </c>
       <c r="B11" t="s">
         <v>48</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>10037</v>
       </c>
       <c r="D11" t="s">
@@ -991,7 +1111,7 @@
       <c r="G11" t="s">
         <v>52</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1826</v>
       </c>
       <c r="I11" t="s">
@@ -1001,14 +1121,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>54</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>5738</v>
       </c>
       <c r="D12" t="s">
@@ -1023,7 +1143,7 @@
       <c r="G12" t="s">
         <v>56</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>2245</v>
       </c>
       <c r="I12" t="s">
@@ -1033,14 +1153,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>5388</v>
       </c>
       <c r="D13" t="s">
@@ -1055,7 +1175,7 @@
       <c r="G13" t="s">
         <v>44</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>2669</v>
       </c>
       <c r="I13" t="s">
@@ -1065,14 +1185,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>60</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>17685</v>
       </c>
       <c r="D14" t="s">
@@ -1087,7 +1207,7 @@
       <c r="G14" t="s">
         <v>14</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>1637</v>
       </c>
       <c r="I14" t="s">
@@ -1097,14 +1217,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>60</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>17664</v>
       </c>
       <c r="D15" t="s">
@@ -1119,7 +1239,7 @@
       <c r="G15" t="s">
         <v>31</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>3369</v>
       </c>
       <c r="I15" t="s">
@@ -1129,14 +1249,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>60</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>7595</v>
       </c>
       <c r="D16" t="s">
@@ -1151,7 +1271,7 @@
       <c r="G16" t="s">
         <v>66</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>4991</v>
       </c>
       <c r="I16" t="s">
@@ -1161,14 +1281,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1697</v>
       </c>
       <c r="D17" t="s">
@@ -1183,7 +1303,7 @@
       <c r="G17" t="s">
         <v>54</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1697</v>
       </c>
       <c r="I17" t="s">
@@ -1193,54 +1313,42 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>68</v>
       </c>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
         <v>68</v>
       </c>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
       <c r="J18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>68</v>
       </c>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" t="s">
         <v>68</v>
       </c>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
       <c r="J19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>70</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>43133</v>
       </c>
       <c r="D20" t="s">
@@ -1255,7 +1363,7 @@
       <c r="G20" t="s">
         <v>31</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>105</v>
       </c>
       <c r="I20" t="s">
@@ -1265,14 +1373,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>70</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>27231</v>
       </c>
       <c r="D21" t="s">
@@ -1287,7 +1395,7 @@
       <c r="G21" t="s">
         <v>14</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>291</v>
       </c>
       <c r="I21" t="s">
@@ -1297,14 +1405,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>70</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>5429</v>
       </c>
       <c r="D22" t="s">
@@ -1319,7 +1427,7 @@
       <c r="G22" t="s">
         <v>66</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>1599</v>
       </c>
       <c r="I22" t="s">
@@ -1329,14 +1437,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>78</v>
       </c>
       <c r="B23" t="s">
         <v>71</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>66266</v>
       </c>
       <c r="D23" t="s">
@@ -1351,7 +1459,7 @@
       <c r="G23" t="s">
         <v>80</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>5161</v>
       </c>
       <c r="I23" t="s">
@@ -1361,14 +1469,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>78</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>62053</v>
       </c>
       <c r="D24" t="s">
@@ -1383,7 +1491,7 @@
       <c r="G24" t="s">
         <v>83</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>5589</v>
       </c>
       <c r="I24" t="s">
@@ -1393,14 +1501,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>78</v>
       </c>
       <c r="B25" t="s">
         <v>85</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>60885</v>
       </c>
       <c r="D25" t="s">
@@ -1415,7 +1523,7 @@
       <c r="G25" t="s">
         <v>54</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>10475</v>
       </c>
       <c r="I25" t="s">
@@ -1425,14 +1533,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>88</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>4123</v>
       </c>
       <c r="D26" t="s">
@@ -1447,7 +1555,7 @@
       <c r="G26" t="s">
         <v>71</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>680</v>
       </c>
       <c r="I26" t="s">
@@ -1457,14 +1565,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>88</v>
       </c>
       <c r="B27" t="s">
         <v>71</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>680</v>
       </c>
       <c r="D27" t="s">
@@ -1479,7 +1587,7 @@
       <c r="G27" t="s">
         <v>89</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>4123</v>
       </c>
       <c r="I27" t="s">
@@ -1489,34 +1597,28 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>88</v>
       </c>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
       <c r="E28" t="s">
         <v>25</v>
       </c>
       <c r="F28" t="s">
         <v>88</v>
       </c>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
       <c r="J28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>92</v>
       </c>
       <c r="B29" t="s">
         <v>93</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>111094</v>
       </c>
       <c r="D29" t="s">
@@ -1531,7 +1633,7 @@
       <c r="G29" t="s">
         <v>95</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>1177</v>
       </c>
       <c r="I29" t="s">
@@ -1541,14 +1643,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>92</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>56284</v>
       </c>
       <c r="D30" t="s">
@@ -1563,7 +1665,7 @@
       <c r="G30" t="s">
         <v>98</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>1402</v>
       </c>
       <c r="I30" t="s">
@@ -1573,14 +1675,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>92</v>
       </c>
       <c r="B31" t="s">
         <v>85</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>52135</v>
       </c>
       <c r="D31" t="s">
@@ -1595,7 +1697,7 @@
       <c r="G31" t="s">
         <v>101</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>2210</v>
       </c>
       <c r="I31" t="s">
@@ -1606,7 +1708,701 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF0D6A6-DD2C-4E17-A38E-F928E2236923}">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="B1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1">
+        <v>11033</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1">
+        <v>886</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2740</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
+        <v>942</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1531</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1379</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1">
+        <v>9475</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1100</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>549</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="1">
+        <v>261</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3003</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1">
+        <v>103</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2937</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1659</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2673</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2673</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10037</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1826</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5738</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2245</v>
+      </c>
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5388</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2669</v>
+      </c>
+      <c r="G14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1">
+        <v>17685</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1637</v>
+      </c>
+      <c r="G15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1">
+        <v>17664</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3369</v>
+      </c>
+      <c r="G16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="1">
+        <v>7595</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4991</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1697</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1697</v>
+      </c>
+      <c r="G18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="1">
+        <v>43133</v>
+      </c>
+      <c r="D21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="1">
+        <v>105</v>
+      </c>
+      <c r="G21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="1">
+        <v>27231</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="1">
+        <v>291</v>
+      </c>
+      <c r="G22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5429</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1599</v>
+      </c>
+      <c r="G23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="1">
+        <v>66266</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5161</v>
+      </c>
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="1">
+        <v>62053</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5589</v>
+      </c>
+      <c r="G25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="1">
+        <v>60885</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="1">
+        <v>10475</v>
+      </c>
+      <c r="G26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4123</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="1">
+        <v>680</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1">
+        <v>680</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" s="1">
+        <v>4123</v>
+      </c>
+      <c r="G28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="1">
+        <v>111094</v>
+      </c>
+      <c r="D30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1177</v>
+      </c>
+      <c r="G30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="1">
+        <v>56284</v>
+      </c>
+      <c r="D31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1402</v>
+      </c>
+      <c r="G31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="1">
+        <v>52135</v>
+      </c>
+      <c r="D32" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2210</v>
+      </c>
+      <c r="G32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>